--- a/ig/DM-MAI-2026/CodeSystem-tre-r347-activite-sanitaire-diverse-regulee.xlsx
+++ b/ig/DM-MAI-2026/CodeSystem-tre-r347-activite-sanitaire-diverse-regulee.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="950">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="963">
   <si>
     <t>Property</t>
   </si>
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r347-activite-sanitaire-diverse-regulee</t>
+    <t>http://hl7.org/fhir/us/example/CodeSystem/tre-r347-activite-sanitaire-diverse-regulee</t>
   </si>
   <si>
     <t>Identifier</t>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260505120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:00:00+01:00</t>
+    <t>2026-06-01T12:00:00.000+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,1860 +124,1863 @@
     <t>Count</t>
   </si>
   <si>
+    <t>461</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Uri</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>parent</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#parent</t>
+  </si>
+  <si>
+    <t>An immediate parent of the concept in the hierarchy</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>dateValid</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
+  </si>
+  <si>
+    <t>date de validité d'un code concept</t>
+  </si>
+  <si>
+    <t>dateTime</t>
+  </si>
+  <si>
+    <t>dateMaj</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
+  </si>
+  <si>
+    <t>Date de mise à jour d'un code concept</t>
+  </si>
+  <si>
+    <t>dateFin</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
+  </si>
+  <si>
+    <t>Date de fin d'exploitation d'un code concept</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#status</t>
+  </si>
+  <si>
+    <t>A code that indicates the status of the concept. Typical values are active, experimental, deprecated, and retired</t>
+  </si>
+  <si>
+    <t>deprecationDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
+  </si>
+  <si>
+    <t>The date at which a concept was deprecated. Concepts that are deprecated but not inactive can still be used, but their use is discouraged, and they should be expected to be made inactive in a future release. Property type is dateTime. Note that the status property may also be used to indicate that a concept is deprecated</t>
+  </si>
+  <si>
+    <t>retirementDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
+  </si>
+  <si>
+    <t>The date at which a concept was retired</t>
+  </si>
+  <si>
+    <t>niveau</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#niveau</t>
+  </si>
+  <si>
+    <t>Permet d'indiquer le niveau hiérarchique du code</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0200</t>
+  </si>
+  <si>
+    <t>Hospitalisation</t>
+  </si>
+  <si>
+    <t>0300</t>
+  </si>
+  <si>
+    <t>Disciplines Spécifiques</t>
+  </si>
+  <si>
+    <t>0400</t>
+  </si>
+  <si>
+    <t>Disciplines Médico-Techniques</t>
+  </si>
+  <si>
+    <t>0500</t>
+  </si>
+  <si>
+    <t>Accueil et Réception des Urgences</t>
+  </si>
+  <si>
+    <t>0600</t>
+  </si>
+  <si>
+    <t>Autres Disciplines Sanitaires</t>
+  </si>
+  <si>
+    <t>0800</t>
+  </si>
+  <si>
+    <t>Lutte contre les Toxicomanies</t>
+  </si>
+  <si>
+    <t>0210</t>
+  </si>
+  <si>
+    <t>Médecine</t>
+  </si>
+  <si>
+    <t>0220</t>
+  </si>
+  <si>
+    <t>Chirurgie</t>
+  </si>
+  <si>
+    <t>0230</t>
+  </si>
+  <si>
+    <t>Gynécologie Obstétrique</t>
+  </si>
+  <si>
+    <t>0240</t>
+  </si>
+  <si>
+    <t>Neuro-chirurgie</t>
+  </si>
+  <si>
+    <t>0260</t>
+  </si>
+  <si>
+    <t>Soins de Suite et de Réadaptation</t>
+  </si>
+  <si>
+    <t>0270</t>
+  </si>
+  <si>
+    <t>Soins de Longue Durée</t>
+  </si>
+  <si>
+    <t>0280</t>
+  </si>
+  <si>
+    <t>Psychiatrie Adulte</t>
+  </si>
+  <si>
+    <t>0290</t>
+  </si>
+  <si>
+    <t>Psychiatrie Infanto-juvénile</t>
+  </si>
+  <si>
+    <t>0310</t>
+  </si>
+  <si>
+    <t>Dialyse</t>
+  </si>
+  <si>
+    <t>0320</t>
+  </si>
+  <si>
+    <t>Chimiothérapie</t>
+  </si>
+  <si>
+    <t>0330</t>
+  </si>
+  <si>
+    <t>Hospitalisation de Jour en Gynéco-Obstétrique</t>
+  </si>
+  <si>
+    <t>0340</t>
+  </si>
+  <si>
+    <t>Prévention, Prophylaxie, Conseil</t>
+  </si>
+  <si>
+    <t>0350</t>
+  </si>
+  <si>
+    <t>Aide aux Insuffisants Respiratoires</t>
+  </si>
+  <si>
+    <t>0360</t>
+  </si>
+  <si>
+    <t>Autres Traitements Spécialisés à Domicile</t>
+  </si>
+  <si>
+    <t>0370</t>
+  </si>
+  <si>
+    <t>structures de psychiatrie hors carte sanitaire</t>
+  </si>
+  <si>
+    <t>0380</t>
+  </si>
+  <si>
+    <t>disciplines de cures thermales</t>
+  </si>
+  <si>
+    <t>0410</t>
+  </si>
+  <si>
+    <t>Blocs Opératoires et Obstétricaux</t>
+  </si>
+  <si>
+    <t>0420</t>
+  </si>
+  <si>
+    <t>Anesthésiologie et Réveil</t>
+  </si>
+  <si>
+    <t>0430</t>
+  </si>
+  <si>
+    <t>Imagerie</t>
+  </si>
+  <si>
+    <t>0440</t>
+  </si>
+  <si>
+    <t>Radiothérapie</t>
+  </si>
+  <si>
+    <t>0450</t>
+  </si>
+  <si>
+    <t>Exploration Fonctionnelle</t>
+  </si>
+  <si>
+    <t>0460</t>
+  </si>
+  <si>
+    <t>Techniques de Rééducation et de Réadaptation Fonctionnelle</t>
+  </si>
+  <si>
+    <t>0470</t>
+  </si>
+  <si>
+    <t>Analyses Médicales Biologiques</t>
+  </si>
+  <si>
+    <t>0480</t>
+  </si>
+  <si>
+    <t>Pharmacie et autres Biens Médicaux</t>
+  </si>
+  <si>
+    <t>0510</t>
+  </si>
+  <si>
+    <t>Urgence</t>
+  </si>
+  <si>
+    <t>0520</t>
+  </si>
+  <si>
+    <t>Urgence Chirurgicale</t>
+  </si>
+  <si>
+    <t>0530</t>
+  </si>
+  <si>
+    <t>SAMU - SMUR</t>
+  </si>
+  <si>
+    <t>0610</t>
+  </si>
+  <si>
+    <t>Services Extérieurs</t>
+  </si>
+  <si>
+    <t>0620</t>
+  </si>
+  <si>
+    <t>Transport des Malades</t>
+  </si>
+  <si>
+    <t>0630</t>
+  </si>
+  <si>
+    <t>Stockage d'Organes et de Produits Humains</t>
+  </si>
+  <si>
+    <t>0640</t>
+  </si>
+  <si>
+    <t>Enseignement et Recherche</t>
+  </si>
+  <si>
+    <t>0660</t>
+  </si>
+  <si>
+    <t>Autres Disciplines</t>
+  </si>
+  <si>
+    <t>0810</t>
+  </si>
+  <si>
+    <t>0820</t>
+  </si>
+  <si>
+    <t>Lutte contre l'Alcoolisme</t>
+  </si>
+  <si>
+    <t>0211</t>
+  </si>
+  <si>
+    <t>Médecine Générale</t>
+  </si>
+  <si>
+    <t>0212</t>
+  </si>
+  <si>
+    <t>Pédiatrie</t>
+  </si>
+  <si>
+    <t>0213</t>
+  </si>
+  <si>
+    <t>Spécialités Médicales</t>
+  </si>
+  <si>
+    <t>0214</t>
+  </si>
+  <si>
+    <t>Réanimation Médicale</t>
+  </si>
+  <si>
+    <t>0215</t>
+  </si>
+  <si>
+    <t>Surveillance Continue Médicale</t>
+  </si>
+  <si>
+    <t>0221</t>
+  </si>
+  <si>
+    <t>Chirurgie Générale</t>
+  </si>
+  <si>
+    <t>0222</t>
+  </si>
+  <si>
+    <t>Chirurgie Infantile</t>
+  </si>
+  <si>
+    <t>0223</t>
+  </si>
+  <si>
+    <t>Spécialités Chirurgicales</t>
+  </si>
+  <si>
+    <t>0224</t>
+  </si>
+  <si>
+    <t>Réanimation Chirurgicale</t>
+  </si>
+  <si>
+    <t>0225</t>
+  </si>
+  <si>
+    <t>Surveillance Continue Chirurgicale</t>
+  </si>
+  <si>
+    <t>0231</t>
+  </si>
+  <si>
+    <t>0241</t>
+  </si>
+  <si>
+    <t>0261</t>
+  </si>
+  <si>
+    <t>Maladie à Evolution Prolongée</t>
+  </si>
+  <si>
+    <t>0262</t>
+  </si>
+  <si>
+    <t>Convalescence, Repos, Régime</t>
+  </si>
+  <si>
+    <t>0263</t>
+  </si>
+  <si>
+    <t>Rééducation Fonctionnelle et Réadaptation</t>
+  </si>
+  <si>
+    <t>0264</t>
+  </si>
+  <si>
+    <t>Lutte contre la Tuberculose et les Maladies Respiratoires</t>
+  </si>
+  <si>
+    <t>0265</t>
+  </si>
+  <si>
+    <t>Cures Thermales</t>
+  </si>
+  <si>
+    <t>0266</t>
+  </si>
+  <si>
+    <t>Cures Médicales</t>
+  </si>
+  <si>
+    <t>0267</t>
+  </si>
+  <si>
+    <t>Cures Médicales pour Enfants</t>
+  </si>
+  <si>
+    <t>0268</t>
+  </si>
+  <si>
+    <t>Post-Cure pour Alcooliques</t>
+  </si>
+  <si>
+    <t>0271</t>
+  </si>
+  <si>
+    <t>0281</t>
+  </si>
+  <si>
+    <t>0291</t>
+  </si>
+  <si>
+    <t>0311</t>
+  </si>
+  <si>
+    <t>0321</t>
+  </si>
+  <si>
+    <t>0331</t>
+  </si>
+  <si>
+    <t>0341</t>
+  </si>
+  <si>
+    <t>Examens Systématique et Dépistage</t>
+  </si>
+  <si>
+    <t>0342</t>
+  </si>
+  <si>
+    <t>Prévention et Conseil</t>
+  </si>
+  <si>
+    <t>0343</t>
+  </si>
+  <si>
+    <t>Soins Divers</t>
+  </si>
+  <si>
+    <t>0351</t>
+  </si>
+  <si>
+    <t>0361</t>
+  </si>
+  <si>
+    <t>0371</t>
+  </si>
+  <si>
+    <t>structures de psychiatrie sans hébergement</t>
+  </si>
+  <si>
+    <t>0372</t>
+  </si>
+  <si>
+    <t>psychiatrie en milieu pénitentiaire</t>
+  </si>
+  <si>
+    <t>0381</t>
+  </si>
+  <si>
+    <t>0411</t>
+  </si>
+  <si>
+    <t>0421</t>
+  </si>
+  <si>
+    <t>0431</t>
+  </si>
+  <si>
+    <t>0441</t>
+  </si>
+  <si>
+    <t>0451</t>
+  </si>
+  <si>
+    <t>0461</t>
+  </si>
+  <si>
+    <t>0471</t>
+  </si>
+  <si>
+    <t>0481</t>
+  </si>
+  <si>
+    <t>Pharmacie et autres biens médicaux</t>
+  </si>
+  <si>
+    <t>0511</t>
+  </si>
+  <si>
+    <t>0521</t>
+  </si>
+  <si>
+    <t>0531</t>
+  </si>
+  <si>
+    <t>0621</t>
+  </si>
+  <si>
+    <t>0631</t>
+  </si>
+  <si>
+    <t>0641</t>
+  </si>
+  <si>
+    <t>Enseignement</t>
+  </si>
+  <si>
+    <t>0642</t>
+  </si>
+  <si>
+    <t>Recherche</t>
+  </si>
+  <si>
+    <t>0661</t>
+  </si>
+  <si>
+    <t>0811</t>
+  </si>
+  <si>
+    <t>0821</t>
+  </si>
+  <si>
+    <t>023</t>
+  </si>
+  <si>
+    <t>Stérilisation</t>
+  </si>
+  <si>
+    <t>034</t>
+  </si>
+  <si>
+    <t>Radiostandard</t>
+  </si>
+  <si>
+    <t>035</t>
+  </si>
+  <si>
+    <t>Scanographie X</t>
+  </si>
+  <si>
+    <t>036</t>
+  </si>
+  <si>
+    <t>Neuroradiologie</t>
+  </si>
+  <si>
+    <t>037</t>
+  </si>
+  <si>
+    <t>Hémodynamique</t>
+  </si>
+  <si>
+    <t>038</t>
+  </si>
+  <si>
+    <t>Radiothérapie de Contact</t>
+  </si>
+  <si>
+    <t>039</t>
+  </si>
+  <si>
+    <t>Radiothérapie Externe(Césium Cobalt)</t>
+  </si>
+  <si>
+    <t>041</t>
+  </si>
+  <si>
+    <t>Radiothérapie Haute Énergie</t>
+  </si>
+  <si>
+    <t>043</t>
+  </si>
+  <si>
+    <t>Curiethérapie</t>
+  </si>
+  <si>
+    <t>044</t>
+  </si>
+  <si>
+    <t>Autre Radiothérapie Spécialisée</t>
+  </si>
+  <si>
+    <t>045</t>
+  </si>
+  <si>
+    <t>Exploration Fonctionnelle Cardiovasculaire</t>
+  </si>
+  <si>
+    <t>046</t>
+  </si>
+  <si>
+    <t>Exploration Fonctionnelle Néphrologique</t>
+  </si>
+  <si>
+    <t>047</t>
+  </si>
+  <si>
+    <t>Exploration Fonctionnelle Pneumologique</t>
+  </si>
+  <si>
+    <t>048</t>
+  </si>
+  <si>
+    <t>Exploration Fonctionnelle Neurologique</t>
+  </si>
+  <si>
+    <t>049</t>
+  </si>
+  <si>
+    <t>Exploration Fonctionnelle Tube Digestif</t>
+  </si>
+  <si>
+    <t>050</t>
+  </si>
+  <si>
+    <t>Exploration Fonctionnelle Fonctionnelle Spécialisée</t>
+  </si>
+  <si>
+    <t>051</t>
+  </si>
+  <si>
+    <t>Exploration Fonctionnelle Cardiovasculaire Néphrologique</t>
+  </si>
+  <si>
+    <t>052</t>
+  </si>
+  <si>
+    <t>Exploration Fonctionnelle Cardiovasculaire Pneumologique.</t>
+  </si>
+  <si>
+    <t>053</t>
+  </si>
+  <si>
+    <t>Exploration Fonctionnelle Fonctionnelle Polyvalente</t>
+  </si>
+  <si>
+    <t>055</t>
+  </si>
+  <si>
+    <t>Réadaption-Rééducation Fonctionnelle Polyvalente</t>
+  </si>
+  <si>
+    <t>056</t>
+  </si>
+  <si>
+    <t>Ergothérapie</t>
+  </si>
+  <si>
+    <t>057</t>
+  </si>
+  <si>
+    <t>Hydrothérapie</t>
+  </si>
+  <si>
+    <t>058</t>
+  </si>
+  <si>
+    <t>Kinésithérapie</t>
+  </si>
+  <si>
+    <t>059</t>
+  </si>
+  <si>
+    <t>Orthophonie</t>
+  </si>
+  <si>
+    <t>060</t>
+  </si>
+  <si>
+    <t>Orthoptie</t>
+  </si>
+  <si>
+    <t>061</t>
+  </si>
+  <si>
+    <t>Autre Rééducation Spécialisée</t>
+  </si>
+  <si>
+    <t>062</t>
+  </si>
+  <si>
+    <t>Anatomie Cytologie Pathologiques</t>
+  </si>
+  <si>
+    <t>063</t>
+  </si>
+  <si>
+    <t>Bactériologie</t>
+  </si>
+  <si>
+    <t>064</t>
+  </si>
+  <si>
+    <t>Biochimie</t>
+  </si>
+  <si>
+    <t>065</t>
+  </si>
+  <si>
+    <t>Biophysique</t>
+  </si>
+  <si>
+    <t>067</t>
+  </si>
+  <si>
+    <t>Coprologie</t>
+  </si>
+  <si>
+    <t>068</t>
+  </si>
+  <si>
+    <t>Cytologie</t>
+  </si>
+  <si>
+    <t>069</t>
+  </si>
+  <si>
+    <t>Cytogénétique</t>
+  </si>
+  <si>
+    <t>070</t>
+  </si>
+  <si>
+    <t>Embryologie</t>
+  </si>
+  <si>
+    <t>071</t>
+  </si>
+  <si>
+    <t>Enzymologie</t>
+  </si>
+  <si>
+    <t>072</t>
+  </si>
+  <si>
+    <t>Hématologie</t>
+  </si>
+  <si>
+    <t>073</t>
+  </si>
+  <si>
+    <t>Histologie</t>
+  </si>
+  <si>
+    <t>074</t>
+  </si>
+  <si>
+    <t>Hormonologie</t>
+  </si>
+  <si>
+    <t>076</t>
+  </si>
+  <si>
+    <t>Immunologie</t>
+  </si>
+  <si>
+    <t>077</t>
+  </si>
+  <si>
+    <t>Bactériologie-Vitro Parasitologie</t>
+  </si>
+  <si>
+    <t>078</t>
+  </si>
+  <si>
+    <t>Mycologie</t>
+  </si>
+  <si>
+    <t>079</t>
+  </si>
+  <si>
+    <t>Parasitologie</t>
+  </si>
+  <si>
+    <t>080</t>
+  </si>
+  <si>
+    <t>Pharmacologie</t>
+  </si>
+  <si>
+    <t>081</t>
+  </si>
+  <si>
+    <t>Sérologie</t>
+  </si>
+  <si>
+    <t>082</t>
+  </si>
+  <si>
+    <t>Toxicologie</t>
+  </si>
+  <si>
+    <t>083</t>
+  </si>
+  <si>
+    <t>Virologie</t>
+  </si>
+  <si>
+    <t>084</t>
+  </si>
+  <si>
+    <t>Biologie Médicale</t>
+  </si>
+  <si>
+    <t>085</t>
+  </si>
+  <si>
+    <t>Autre discipline de biologie médicale spécialisée</t>
+  </si>
+  <si>
+    <t>086</t>
+  </si>
+  <si>
+    <t>Activité de vaccination gratuite</t>
+  </si>
+  <si>
+    <t>087</t>
+  </si>
+  <si>
+    <t>Consultation Anti-Tabac</t>
+  </si>
+  <si>
+    <t>088</t>
+  </si>
+  <si>
+    <t>Médecine Légale</t>
+  </si>
+  <si>
+    <t>089</t>
+  </si>
+  <si>
+    <t>Médecine Préventive Santé Publique</t>
+  </si>
+  <si>
+    <t>090</t>
+  </si>
+  <si>
+    <t>Autres Consultations Soins Externes</t>
+  </si>
+  <si>
+    <t>091</t>
+  </si>
+  <si>
+    <t>Fabrication Préparation Produits Pharmaceutiques</t>
+  </si>
+  <si>
+    <t>092</t>
+  </si>
+  <si>
+    <t>Distribution de Produits Pharmaceutiques</t>
+  </si>
+  <si>
+    <t>093</t>
+  </si>
+  <si>
+    <t>Distribution autres Biens Médicaux</t>
+  </si>
+  <si>
+    <t>094</t>
+  </si>
+  <si>
+    <t>Pharmacocinétique</t>
+  </si>
+  <si>
+    <t>095</t>
+  </si>
+  <si>
+    <t>Fabrication Autres Biens Médicaux Prothèses</t>
+  </si>
+  <si>
+    <t>096</t>
+  </si>
+  <si>
+    <t>Prélèvement Scientifique Vérification Diagnostic</t>
+  </si>
+  <si>
+    <t>097</t>
+  </si>
+  <si>
+    <t>Anesthésiologie</t>
+  </si>
+  <si>
+    <t>098</t>
+  </si>
+  <si>
+    <t>Parasitologie et Mycologie</t>
+  </si>
+  <si>
+    <t>099</t>
+  </si>
+  <si>
+    <t>Activité Pharmaco-Toxico-Vigilance</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>Radio-Immunologie</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>Médecine Générale ou Médecine Interne</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>Maladie Infectieuse et Parasitaire</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>Centre AntiPoison</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>Réanimation Médicale Adultes</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>Réanimation Polyvalente</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>SURVEILLANCE CONTINUE POLYV.</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>Médecine de l'Adolescent</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>PEDIATRIE NOURRISSONS</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>Néonatalogie</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>Médecine Gériatrique</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>ALLERGOLOGIE</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>Dermatologie-Vénérologie</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>Endocrino-Diabetologie</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>Maladies Métaboliques Nutrition</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>Hématologie Maladies du Sang</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>Hépato-Gastro-Entérologie</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>MEDECINE CARCINOLOGIQUE</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>Médecine Cardio-Vasculaire</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>Neurologie</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>Pneumologie</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>Rhumatologie</t>
+  </si>
+  <si>
+    <t>134</t>
+  </si>
+  <si>
+    <t>RADIOTHER. &amp; MEDEC. NUCLEAIRE</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>RADIOTHERAPIE</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>Médecine Nucléaire</t>
+  </si>
+  <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>Réanimation Chirurgicale Adultes</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>SPECIALITE CHIRURGICALE</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>Chirurgie Carcinologie</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>Traitement des Grands Brûlés</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>Chirurgie Digestive</t>
+  </si>
+  <si>
+    <t>147</t>
+  </si>
+  <si>
+    <t>Chirurgie Thoracique Cardio-Vasculaire</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>CHIRURGIE THORACO-PULMONAIRE</t>
+  </si>
+  <si>
+    <t>149</t>
+  </si>
+  <si>
+    <t>Chirurgie Vasculaire</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>CHIRURGIE CARDIO-VASCULAIRE</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>Neurochirurgie</t>
+  </si>
+  <si>
+    <t>152</t>
+  </si>
+  <si>
+    <t>Orthopédie-Traumatologie</t>
+  </si>
+  <si>
+    <t>153</t>
+  </si>
+  <si>
+    <t>Actes d'explantation de prothèses PIP</t>
+  </si>
+  <si>
+    <t>154</t>
+  </si>
+  <si>
+    <t>Chirurgie Plastique Reconstructive</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>ORL ET OPHTALMOLOGIE</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>Oto-rhino-laryngologie</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>Ophtalmologie</t>
+  </si>
+  <si>
+    <t>158</t>
+  </si>
+  <si>
+    <t>Stomatologie Chirurgie Maxillo-faciale</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>Stomatologie</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>Urologie</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t>ORL-OPHTALMOLOG.&amp; STOMATOLOGIE</t>
+  </si>
+  <si>
+    <t>163</t>
+  </si>
+  <si>
+    <t>Gynéco.&amp; Obstétrique</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>Gynécologie Médicale</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>Chroniques Convalescence Indifférencié</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>Chroniques</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>Repos-Convalescence Régime Indifférencié</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>Repos</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>Convalescence</t>
+  </si>
+  <si>
+    <t>171</t>
+  </si>
+  <si>
+    <t>Régime</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>Rééducation Fonctionnelle Réadaptation Polyvalente</t>
+  </si>
+  <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>Cure Thermale</t>
+  </si>
+  <si>
+    <t>174</t>
+  </si>
+  <si>
+    <t>MEDEC.GEN. &amp; SPECIALITE MEDIC.</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>Long Séjour Personnes Ayant Perdu Leur Autonomie de Vie</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>Rééducation Fonctionnelle Réadaptation Motrice</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>Rééducation Fonctionnelle Réadaptation Neurologique</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>Rééducation des Affections Respiratoires</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>Chirurgie Générale Spécialités Chirurgicales</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>Rééducat. Maladies Cardio-Vasculaires</t>
+  </si>
+  <si>
+    <t>183</t>
+  </si>
+  <si>
+    <t>OBSTETRIQUE SANS CHIRURGIE</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>Rééducation des Affections Hépato-Digestives</t>
+  </si>
+  <si>
+    <t>185</t>
+  </si>
+  <si>
+    <t>Repos-Convalescence Indifférenciés</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>REEDUCATION PERSONNE AGEE</t>
+  </si>
+  <si>
+    <t>187</t>
+  </si>
+  <si>
+    <t>Rééducation Fonctionnelle Réadaptation</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>Cure Thermale des Voies Respiratoires</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>CURE THERM.AFFECT.HEPATO-DIGES</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>CURE THERM.APPAREIL URINAIRE</t>
+  </si>
+  <si>
+    <t>193</t>
+  </si>
+  <si>
+    <t>Cure Thermale Rhumatologie Séquel.Traum.Ostéo-articaires</t>
+  </si>
+  <si>
+    <t>194</t>
+  </si>
+  <si>
+    <t>Cure Thermale en Dermatologie</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>Soins aux Toxicomanes</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>Lutte Contre l'Alcoolisme</t>
+  </si>
+  <si>
+    <t>197</t>
+  </si>
+  <si>
+    <t>Activité dentaire unique</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>Oncologie</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>Transfusion Sanguine (Laboratoire)</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>Banque de Sperme</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>Banque d'Organes</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>Dispensaire de Soins</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>Activité infirmière unique</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>Act inform dépistage diag infections sexuellmnt transmissibl</t>
+  </si>
+  <si>
+    <t>206</t>
+  </si>
+  <si>
+    <t>Lutte Antihansénienne</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>S.A.M.U Centre 15</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>S.M.U.R. U.M.H.</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>Ambulances</t>
+  </si>
+  <si>
+    <t>211</t>
+  </si>
+  <si>
+    <t>Accueil et Traitement des Urgences Médico-Chirurgicales</t>
+  </si>
+  <si>
+    <t>214</t>
+  </si>
+  <si>
+    <t>Postcure pour Alcooliques</t>
+  </si>
+  <si>
+    <t>217</t>
+  </si>
+  <si>
+    <t>Lutte Contre La Tuberculose Indifférenciée</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>Activité de lutte anti tuberculose</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>Lutte Ctre la Tuberculose Pulmonaire</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>Lutte Ctre Tuberculose Extra-Pulmonaire</t>
+  </si>
+  <si>
+    <t>221</t>
+  </si>
+  <si>
+    <t>Cure et Repos en Prévention</t>
+  </si>
+  <si>
+    <t>222</t>
+  </si>
+  <si>
+    <t>Traitements Préventifs de la Tuberculose</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>Médecine Générale ou Polyvalente</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>Observation et Traitement Pneumoconioses</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>Médecine Interne Spécialités Médicales</t>
+  </si>
+  <si>
+    <t>226</t>
+  </si>
+  <si>
+    <t>Accueil Orientation. des Malades.Tuberculo Pulmonaires</t>
+  </si>
+  <si>
+    <t>227</t>
+  </si>
+  <si>
+    <t>Postcure pour Tuberculeux</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Psychiatrie Générale</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>centre médico-psychologique adulte</t>
+  </si>
+  <si>
+    <t>232</t>
+  </si>
+  <si>
+    <t>centre médico-psychologique infanto-juvénile</t>
+  </si>
+  <si>
+    <t>233</t>
+  </si>
+  <si>
+    <t>Centre d'accueil thérapeutique à temps partiel adulte</t>
+  </si>
+  <si>
+    <t>234</t>
+  </si>
+  <si>
+    <t>Centre d'accueil thérapeutique à temps partiel infanto-juv</t>
+  </si>
+  <si>
+    <t>235</t>
+  </si>
+  <si>
+    <t>soins intensifs de néonatologie</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>Psychiatrie Infanto-Juvenile</t>
+  </si>
+  <si>
+    <t>237</t>
+  </si>
+  <si>
+    <t>centre d'accueil permanent adulte</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>centre d'accueil permanent infanto-juvénile</t>
+  </si>
+  <si>
+    <t>240</t>
+  </si>
+  <si>
+    <t>POST-CURE POUR TOXICOMANES</t>
+  </si>
+  <si>
+    <t>241</t>
+  </si>
+  <si>
+    <t>Hygiène Alimentaire</t>
+  </si>
+  <si>
+    <t>244</t>
+  </si>
+  <si>
+    <t>hospitalisation psychiatrique à domicile adulte</t>
+  </si>
+  <si>
+    <t>245</t>
+  </si>
+  <si>
+    <t>hospitalisation psychiatrique à domicile infanto-juv</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>Pouponnière à Caractère Sanitaire</t>
+  </si>
+  <si>
+    <t>263</t>
+  </si>
+  <si>
+    <t>Placement familial sanitaire</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>COLONIE A CARACTERE SANITAIRE</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>CHIMIOTHER.EN HEMATOL.&amp; CANCER</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>Urgence Médicale</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>Urgence Chirurgicale (SERV.PORTE)</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>Urgence Indifférenciée</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>Interruption Volontaire de Grossesse</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Examens de Santé et Bilans</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>Néphrologie</t>
+  </si>
+  <si>
+    <t>362</t>
+  </si>
+  <si>
+    <t>Chirurgie Obstétrique Indifférenciées</t>
+  </si>
+  <si>
+    <t>384</t>
+  </si>
+  <si>
+    <t>Protection Maternelle &amp; Infantile</t>
+  </si>
+  <si>
+    <t>385</t>
+  </si>
+  <si>
+    <t>Consultations Prénuptiale Prénatale et Postnatale</t>
+  </si>
+  <si>
+    <t>386</t>
+  </si>
+  <si>
+    <t>Consultations Protection Infantile</t>
+  </si>
+  <si>
+    <t>387</t>
+  </si>
+  <si>
+    <t>Consultations de Nourrissons</t>
+  </si>
+  <si>
+    <t>388</t>
+  </si>
+  <si>
+    <t>Consultations de deuxième age</t>
+  </si>
+  <si>
+    <t>389</t>
+  </si>
+  <si>
+    <t>Lutte contre la Stérilité</t>
+  </si>
+  <si>
+    <t>390</t>
+  </si>
+  <si>
+    <t>Consultation en Conseil Génétique</t>
+  </si>
+  <si>
+    <t>391</t>
+  </si>
+  <si>
+    <t>Consultation de Planification ou Éducation Familiale</t>
+  </si>
+  <si>
+    <t>392</t>
+  </si>
+  <si>
+    <t>Information Consultation ou Conseil familial</t>
+  </si>
+  <si>
+    <t>394</t>
+  </si>
+  <si>
+    <t>Lactarium</t>
+  </si>
+  <si>
+    <t>395</t>
+  </si>
+  <si>
+    <t>Guidance Parentale</t>
+  </si>
+  <si>
+    <t>396</t>
+  </si>
+  <si>
+    <t>Guidance infantile</t>
+  </si>
+  <si>
+    <t>401</t>
+  </si>
+  <si>
+    <t>unité de proximité accueil traitement orientation urgences</t>
+  </si>
+  <si>
+    <t>402</t>
+  </si>
+  <si>
+    <t>service accueil et traitement urgences</t>
+  </si>
+  <si>
+    <t>403</t>
+  </si>
+  <si>
+    <t>pôle spécialisé urgence en pédiatrie</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>pôle spécialisé urgence en ophtalmologie</t>
+  </si>
+  <si>
+    <t>405</t>
+  </si>
+  <si>
+    <t>pôle spécialisé urgence en cardiologie</t>
+  </si>
+  <si>
+    <t>406</t>
+  </si>
+  <si>
+    <t>pôle spécialisé urgence en traumatologie</t>
+  </si>
+  <si>
+    <t>407</t>
+  </si>
+  <si>
+    <t>pôle spécialisé urgence en SOS main</t>
+  </si>
+  <si>
+    <t>408</t>
+  </si>
+  <si>
+    <t>pôle spécialisé urgence en neurochirurgie</t>
+  </si>
+  <si>
+    <t>409</t>
+  </si>
+  <si>
+    <t>autre pôle spécialisé urgence non dénommé ailleurs</t>
+  </si>
+  <si>
+    <t>446</t>
+  </si>
+  <si>
+    <t>Médecine Scolaire</t>
+  </si>
+  <si>
+    <t>447</t>
+  </si>
+  <si>
+    <t>Médecine Universitaire</t>
+  </si>
+  <si>
+    <t>448</t>
+  </si>
+  <si>
+    <t>Médecine Sportive</t>
+  </si>
+  <si>
+    <t>452</t>
+  </si>
+  <si>
+    <t>Aide Aux Insuffisants Respiratoires</t>
+  </si>
+  <si>
     <t>457</t>
   </si>
   <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Uri</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>parent</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#parent</t>
-  </si>
-  <si>
-    <t>An immediate parent of the concept in the hierarchy</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>dateValid</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
-  </si>
-  <si>
-    <t>date de validité d'un code concept</t>
-  </si>
-  <si>
-    <t>dateTime</t>
-  </si>
-  <si>
-    <t>dateMaj</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
-  </si>
-  <si>
-    <t>Date de mise à jour d'un code concept</t>
-  </si>
-  <si>
-    <t>dateFin</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
-  </si>
-  <si>
-    <t>Date de fin d'exploitation d'un code concept</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#status</t>
-  </si>
-  <si>
-    <t>A code that indicates the status of the concept. Typical values are active, experimental, deprecated, and retired</t>
-  </si>
-  <si>
-    <t>deprecationDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
-  </si>
-  <si>
-    <t>The date at which a concept was deprecated. Concepts that are deprecated but not inactive can still be used, but their use is discouraged, and they should be expected to be made inactive in a future release. Property type is dateTime. Note that the status property may also be used to indicate that a concept is deprecated</t>
-  </si>
-  <si>
-    <t>retirementDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
-  </si>
-  <si>
-    <t>The date at which a concept was retired</t>
-  </si>
-  <si>
-    <t>niveau</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#niveau</t>
-  </si>
-  <si>
-    <t>Permet d'indiquer le niveau hiérarchique du code</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>0200</t>
-  </si>
-  <si>
-    <t>Hospitalisation</t>
-  </si>
-  <si>
-    <t>0300</t>
-  </si>
-  <si>
-    <t>Disciplines Spécifiques</t>
-  </si>
-  <si>
-    <t>0400</t>
-  </si>
-  <si>
-    <t>Disciplines Médico-Techniques</t>
-  </si>
-  <si>
-    <t>0500</t>
-  </si>
-  <si>
-    <t>Accueil et Réception des Urgences</t>
-  </si>
-  <si>
-    <t>0600</t>
-  </si>
-  <si>
-    <t>Autres Disciplines Sanitaires</t>
-  </si>
-  <si>
-    <t>0800</t>
-  </si>
-  <si>
-    <t>Lutte contre les Toxicomanies</t>
-  </si>
-  <si>
-    <t>0210</t>
-  </si>
-  <si>
-    <t>Médecine</t>
-  </si>
-  <si>
-    <t>0220</t>
-  </si>
-  <si>
-    <t>Chirurgie</t>
-  </si>
-  <si>
-    <t>0230</t>
-  </si>
-  <si>
-    <t>Gynécologie Obstétrique</t>
-  </si>
-  <si>
-    <t>0240</t>
-  </si>
-  <si>
-    <t>Neuro-chirurgie</t>
-  </si>
-  <si>
-    <t>0260</t>
-  </si>
-  <si>
-    <t>Soins de Suite et de Réadaptation</t>
-  </si>
-  <si>
-    <t>0270</t>
-  </si>
-  <si>
-    <t>Soins de Longue Durée</t>
-  </si>
-  <si>
-    <t>0280</t>
-  </si>
-  <si>
-    <t>Psychiatrie Adulte</t>
-  </si>
-  <si>
-    <t>0290</t>
-  </si>
-  <si>
-    <t>Psychiatrie Infanto-juvénile</t>
-  </si>
-  <si>
-    <t>0310</t>
-  </si>
-  <si>
-    <t>Dialyse</t>
-  </si>
-  <si>
-    <t>0320</t>
-  </si>
-  <si>
-    <t>Chimiothérapie</t>
-  </si>
-  <si>
-    <t>0330</t>
-  </si>
-  <si>
-    <t>Hospitalisation de Jour en Gynéco-Obstétrique</t>
-  </si>
-  <si>
-    <t>0340</t>
-  </si>
-  <si>
-    <t>Prévention, Prophylaxie, Conseil</t>
-  </si>
-  <si>
-    <t>0350</t>
-  </si>
-  <si>
-    <t>Aide aux Insuffisants Respiratoires</t>
-  </si>
-  <si>
-    <t>0360</t>
-  </si>
-  <si>
-    <t>Autres Traitements Spécialisés à Domicile</t>
-  </si>
-  <si>
-    <t>0370</t>
-  </si>
-  <si>
-    <t>structures de psychiatrie hors carte sanitaire</t>
-  </si>
-  <si>
-    <t>0380</t>
-  </si>
-  <si>
-    <t>disciplines de cures thermales</t>
-  </si>
-  <si>
-    <t>0410</t>
-  </si>
-  <si>
-    <t>Blocs Opératoires et Obstétricaux</t>
-  </si>
-  <si>
-    <t>0420</t>
-  </si>
-  <si>
-    <t>Anesthésiologie et Réveil</t>
-  </si>
-  <si>
-    <t>0430</t>
-  </si>
-  <si>
-    <t>Imagerie</t>
-  </si>
-  <si>
-    <t>0440</t>
-  </si>
-  <si>
-    <t>Radiothérapie</t>
-  </si>
-  <si>
-    <t>0450</t>
-  </si>
-  <si>
-    <t>Exploration Fonctionnelle</t>
-  </si>
-  <si>
-    <t>0460</t>
-  </si>
-  <si>
-    <t>Techniques de Rééducation et de Réadaptation Fonctionnelle</t>
-  </si>
-  <si>
-    <t>0470</t>
-  </si>
-  <si>
-    <t>Analyses Médicales Biologiques</t>
-  </si>
-  <si>
-    <t>0480</t>
-  </si>
-  <si>
-    <t>Pharmacie et autres Biens Médicaux</t>
-  </si>
-  <si>
-    <t>0510</t>
-  </si>
-  <si>
-    <t>Urgence</t>
-  </si>
-  <si>
-    <t>0520</t>
-  </si>
-  <si>
-    <t>Urgence Chirurgicale</t>
-  </si>
-  <si>
-    <t>0530</t>
-  </si>
-  <si>
-    <t>SAMU - SMUR</t>
-  </si>
-  <si>
-    <t>0610</t>
-  </si>
-  <si>
-    <t>Services Extérieurs</t>
-  </si>
-  <si>
-    <t>0620</t>
-  </si>
-  <si>
-    <t>Transport des Malades</t>
-  </si>
-  <si>
-    <t>0630</t>
-  </si>
-  <si>
-    <t>Stockage d'Organes et de Produits Humains</t>
-  </si>
-  <si>
-    <t>0640</t>
-  </si>
-  <si>
-    <t>Enseignement et Recherche</t>
-  </si>
-  <si>
-    <t>0660</t>
-  </si>
-  <si>
-    <t>Autres Disciplines</t>
-  </si>
-  <si>
-    <t>0810</t>
-  </si>
-  <si>
-    <t>0820</t>
-  </si>
-  <si>
-    <t>Lutte contre l'Alcoolisme</t>
-  </si>
-  <si>
-    <t>0211</t>
-  </si>
-  <si>
-    <t>Médecine Générale</t>
-  </si>
-  <si>
-    <t>0212</t>
-  </si>
-  <si>
-    <t>Pédiatrie</t>
-  </si>
-  <si>
-    <t>0213</t>
-  </si>
-  <si>
-    <t>Spécialités Médicales</t>
-  </si>
-  <si>
-    <t>0214</t>
-  </si>
-  <si>
-    <t>Réanimation Médicale</t>
-  </si>
-  <si>
-    <t>0215</t>
-  </si>
-  <si>
-    <t>Surveillance Continue Médicale</t>
-  </si>
-  <si>
-    <t>0221</t>
-  </si>
-  <si>
-    <t>Chirurgie Générale</t>
-  </si>
-  <si>
-    <t>0222</t>
-  </si>
-  <si>
-    <t>Chirurgie Infantile</t>
-  </si>
-  <si>
-    <t>0223</t>
-  </si>
-  <si>
-    <t>Spécialités Chirurgicales</t>
-  </si>
-  <si>
-    <t>0224</t>
-  </si>
-  <si>
-    <t>Réanimation Chirurgicale</t>
-  </si>
-  <si>
-    <t>0225</t>
-  </si>
-  <si>
-    <t>Surveillance Continue Chirurgicale</t>
-  </si>
-  <si>
-    <t>0231</t>
-  </si>
-  <si>
-    <t>0241</t>
-  </si>
-  <si>
-    <t>0261</t>
-  </si>
-  <si>
-    <t>Maladie à Evolution Prolongée</t>
-  </si>
-  <si>
-    <t>0262</t>
-  </si>
-  <si>
-    <t>Convalescence, Repos, Régime</t>
-  </si>
-  <si>
-    <t>0263</t>
-  </si>
-  <si>
-    <t>Rééducation Fonctionnelle et Réadaptation</t>
-  </si>
-  <si>
-    <t>0264</t>
-  </si>
-  <si>
-    <t>Lutte contre la Tuberculose et les Maladies Respiratoires</t>
-  </si>
-  <si>
-    <t>0265</t>
-  </si>
-  <si>
-    <t>Cures Thermales</t>
-  </si>
-  <si>
-    <t>0266</t>
-  </si>
-  <si>
-    <t>Cures Médicales</t>
-  </si>
-  <si>
-    <t>0267</t>
-  </si>
-  <si>
-    <t>Cures Médicales pour Enfants</t>
-  </si>
-  <si>
-    <t>0268</t>
-  </si>
-  <si>
-    <t>Post-Cure pour Alcooliques</t>
-  </si>
-  <si>
-    <t>0271</t>
-  </si>
-  <si>
-    <t>0281</t>
-  </si>
-  <si>
-    <t>0291</t>
-  </si>
-  <si>
-    <t>0311</t>
-  </si>
-  <si>
-    <t>0321</t>
-  </si>
-  <si>
-    <t>0331</t>
-  </si>
-  <si>
-    <t>0341</t>
-  </si>
-  <si>
-    <t>Examens Systématique et Dépistage</t>
-  </si>
-  <si>
-    <t>0342</t>
-  </si>
-  <si>
-    <t>Prévention et Conseil</t>
-  </si>
-  <si>
-    <t>0343</t>
-  </si>
-  <si>
-    <t>Soins Divers</t>
-  </si>
-  <si>
-    <t>0351</t>
-  </si>
-  <si>
-    <t>0361</t>
-  </si>
-  <si>
-    <t>0371</t>
-  </si>
-  <si>
-    <t>structures de psychiatrie sans hébergement</t>
-  </si>
-  <si>
-    <t>0372</t>
-  </si>
-  <si>
-    <t>psychiatrie en milieu pénitentiaire</t>
-  </si>
-  <si>
-    <t>0381</t>
-  </si>
-  <si>
-    <t>0411</t>
-  </si>
-  <si>
-    <t>0421</t>
-  </si>
-  <si>
-    <t>0431</t>
-  </si>
-  <si>
-    <t>0441</t>
-  </si>
-  <si>
-    <t>0451</t>
-  </si>
-  <si>
-    <t>0461</t>
-  </si>
-  <si>
-    <t>0471</t>
-  </si>
-  <si>
-    <t>0481</t>
-  </si>
-  <si>
-    <t>Pharmacie et autres biens médicaux</t>
-  </si>
-  <si>
-    <t>0511</t>
-  </si>
-  <si>
-    <t>0521</t>
-  </si>
-  <si>
-    <t>0531</t>
-  </si>
-  <si>
-    <t>0621</t>
-  </si>
-  <si>
-    <t>0631</t>
-  </si>
-  <si>
-    <t>0641</t>
-  </si>
-  <si>
-    <t>Enseignement</t>
-  </si>
-  <si>
-    <t>0642</t>
-  </si>
-  <si>
-    <t>Recherche</t>
-  </si>
-  <si>
-    <t>0661</t>
-  </si>
-  <si>
-    <t>0811</t>
-  </si>
-  <si>
-    <t>0821</t>
-  </si>
-  <si>
-    <t>023</t>
-  </si>
-  <si>
-    <t>Stérilisation</t>
-  </si>
-  <si>
-    <t>034</t>
-  </si>
-  <si>
-    <t>Radiostandard</t>
-  </si>
-  <si>
-    <t>035</t>
-  </si>
-  <si>
-    <t>Scanographie X</t>
-  </si>
-  <si>
-    <t>036</t>
-  </si>
-  <si>
-    <t>Neuroradiologie</t>
-  </si>
-  <si>
-    <t>037</t>
-  </si>
-  <si>
-    <t>Hémodynamique</t>
-  </si>
-  <si>
-    <t>038</t>
-  </si>
-  <si>
-    <t>Radiothérapie de Contact</t>
-  </si>
-  <si>
-    <t>039</t>
-  </si>
-  <si>
-    <t>Radiothérapie Externe(Césium Cobalt)</t>
-  </si>
-  <si>
-    <t>041</t>
-  </si>
-  <si>
-    <t>Radiothérapie Haute Énergie</t>
-  </si>
-  <si>
-    <t>043</t>
-  </si>
-  <si>
-    <t>Curiethérapie</t>
-  </si>
-  <si>
-    <t>044</t>
-  </si>
-  <si>
-    <t>Autre Radiothérapie Spécialisée</t>
-  </si>
-  <si>
-    <t>045</t>
-  </si>
-  <si>
-    <t>Exploration Fonctionnelle Cardiovasculaire</t>
-  </si>
-  <si>
-    <t>046</t>
-  </si>
-  <si>
-    <t>Exploration Fonctionnelle Néphrologique</t>
-  </si>
-  <si>
-    <t>047</t>
-  </si>
-  <si>
-    <t>Exploration Fonctionnelle Pneumologique</t>
-  </si>
-  <si>
-    <t>048</t>
-  </si>
-  <si>
-    <t>Exploration Fonctionnelle Neurologique</t>
-  </si>
-  <si>
-    <t>049</t>
-  </si>
-  <si>
-    <t>Exploration Fonctionnelle Tube Digestif</t>
-  </si>
-  <si>
-    <t>050</t>
-  </si>
-  <si>
-    <t>Exploration Fonctionnelle Fonctionnelle Spécialisée</t>
-  </si>
-  <si>
-    <t>051</t>
-  </si>
-  <si>
-    <t>Exploration Fonctionnelle Cardiovasculaire Néphrologique</t>
-  </si>
-  <si>
-    <t>052</t>
-  </si>
-  <si>
-    <t>Exploration Fonctionnelle Cardiovasculaire Pneumologique.</t>
-  </si>
-  <si>
-    <t>053</t>
-  </si>
-  <si>
-    <t>Exploration Fonctionnelle Fonctionnelle Polyvalente</t>
-  </si>
-  <si>
-    <t>055</t>
-  </si>
-  <si>
-    <t>Réadaption-Rééducation Fonctionnelle Polyvalente</t>
-  </si>
-  <si>
-    <t>056</t>
-  </si>
-  <si>
-    <t>Ergothérapie</t>
-  </si>
-  <si>
-    <t>057</t>
-  </si>
-  <si>
-    <t>Hydrothérapie</t>
-  </si>
-  <si>
-    <t>058</t>
-  </si>
-  <si>
-    <t>Kinésithérapie</t>
-  </si>
-  <si>
-    <t>059</t>
-  </si>
-  <si>
-    <t>Orthophonie</t>
-  </si>
-  <si>
-    <t>060</t>
-  </si>
-  <si>
-    <t>Orthoptie</t>
-  </si>
-  <si>
-    <t>061</t>
-  </si>
-  <si>
-    <t>Autre Rééducation Spécialisée</t>
-  </si>
-  <si>
-    <t>062</t>
-  </si>
-  <si>
-    <t>Anatomie Cytologie Pathologiques</t>
-  </si>
-  <si>
-    <t>063</t>
-  </si>
-  <si>
-    <t>Bactériologie</t>
-  </si>
-  <si>
-    <t>064</t>
-  </si>
-  <si>
-    <t>Biochimie</t>
-  </si>
-  <si>
-    <t>065</t>
-  </si>
-  <si>
-    <t>Biophysique</t>
-  </si>
-  <si>
-    <t>067</t>
-  </si>
-  <si>
-    <t>Coprologie</t>
-  </si>
-  <si>
-    <t>068</t>
-  </si>
-  <si>
-    <t>Cytologie</t>
-  </si>
-  <si>
-    <t>069</t>
-  </si>
-  <si>
-    <t>Cytogénétique</t>
-  </si>
-  <si>
-    <t>070</t>
-  </si>
-  <si>
-    <t>Embryologie</t>
-  </si>
-  <si>
-    <t>071</t>
-  </si>
-  <si>
-    <t>Enzymologie</t>
-  </si>
-  <si>
-    <t>072</t>
-  </si>
-  <si>
-    <t>Hématologie</t>
-  </si>
-  <si>
-    <t>073</t>
-  </si>
-  <si>
-    <t>Histologie</t>
-  </si>
-  <si>
-    <t>074</t>
-  </si>
-  <si>
-    <t>Hormonologie</t>
-  </si>
-  <si>
-    <t>076</t>
-  </si>
-  <si>
-    <t>Immunologie</t>
-  </si>
-  <si>
-    <t>077</t>
-  </si>
-  <si>
-    <t>Bactériologie-Vitro Parasitologie</t>
-  </si>
-  <si>
-    <t>078</t>
-  </si>
-  <si>
-    <t>Mycologie</t>
-  </si>
-  <si>
-    <t>079</t>
-  </si>
-  <si>
-    <t>Parasitologie</t>
-  </si>
-  <si>
-    <t>080</t>
-  </si>
-  <si>
-    <t>Pharmacologie</t>
-  </si>
-  <si>
-    <t>081</t>
-  </si>
-  <si>
-    <t>Sérologie</t>
-  </si>
-  <si>
-    <t>082</t>
-  </si>
-  <si>
-    <t>Toxicologie</t>
-  </si>
-  <si>
-    <t>083</t>
-  </si>
-  <si>
-    <t>Virologie</t>
-  </si>
-  <si>
-    <t>084</t>
-  </si>
-  <si>
-    <t>Biologie Médicale</t>
-  </si>
-  <si>
-    <t>085</t>
-  </si>
-  <si>
-    <t>Autre discipline de biologie médicale spécialisée</t>
-  </si>
-  <si>
-    <t>086</t>
-  </si>
-  <si>
-    <t>Activité de vaccination gratuite</t>
-  </si>
-  <si>
-    <t>087</t>
-  </si>
-  <si>
-    <t>Consultation Anti-Tabac</t>
-  </si>
-  <si>
-    <t>088</t>
-  </si>
-  <si>
-    <t>Médecine Légale</t>
-  </si>
-  <si>
-    <t>089</t>
-  </si>
-  <si>
-    <t>Médecine Préventive Santé Publique</t>
-  </si>
-  <si>
-    <t>090</t>
-  </si>
-  <si>
-    <t>Autres Consultations Soins Externes</t>
-  </si>
-  <si>
-    <t>091</t>
-  </si>
-  <si>
-    <t>Fabrication Préparation Produits Pharmaceutiques</t>
-  </si>
-  <si>
-    <t>092</t>
-  </si>
-  <si>
-    <t>Distribution de Produits Pharmaceutiques</t>
-  </si>
-  <si>
-    <t>093</t>
-  </si>
-  <si>
-    <t>Distribution autres Biens Médicaux</t>
-  </si>
-  <si>
-    <t>094</t>
-  </si>
-  <si>
-    <t>Pharmacocinétique</t>
-  </si>
-  <si>
-    <t>095</t>
-  </si>
-  <si>
-    <t>Fabrication Autres Biens Médicaux Prothèses</t>
-  </si>
-  <si>
-    <t>096</t>
-  </si>
-  <si>
-    <t>Prélèvement Scientifique Vérification Diagnostic</t>
-  </si>
-  <si>
-    <t>097</t>
-  </si>
-  <si>
-    <t>Anesthésiologie</t>
-  </si>
-  <si>
-    <t>098</t>
-  </si>
-  <si>
-    <t>Parasitologie et Mycologie</t>
-  </si>
-  <si>
-    <t>099</t>
-  </si>
-  <si>
-    <t>Activité Pharmaco-Toxico-Vigilance</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>Radio-Immunologie</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>Médecine Générale ou Médecine Interne</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>Maladie Infectieuse et Parasitaire</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>Centre AntiPoison</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>Réanimation Médicale Adultes</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>Réanimation Polyvalente</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>SURVEILLANCE CONTINUE POLYV.</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>Médecine de l'Adolescent</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>PEDIATRIE NOURRISSONS</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>Néonatalogie</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>Médecine Gériatrique</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>ALLERGOLOGIE</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>Dermatologie-Vénérologie</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>Endocrino-Diabetologie</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>Maladies Métaboliques Nutrition</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>Hématologie Maladies du Sang</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>Hépato-Gastro-Entérologie</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>MEDECINE CARCINOLOGIQUE</t>
-  </si>
-  <si>
-    <t>127</t>
-  </si>
-  <si>
-    <t>Médecine Cardio-Vasculaire</t>
-  </si>
-  <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>Neurologie</t>
-  </si>
-  <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>Pneumologie</t>
-  </si>
-  <si>
-    <t>133</t>
-  </si>
-  <si>
-    <t>Rhumatologie</t>
-  </si>
-  <si>
-    <t>134</t>
-  </si>
-  <si>
-    <t>RADIOTHER. &amp; MEDEC. NUCLEAIRE</t>
-  </si>
-  <si>
-    <t>135</t>
-  </si>
-  <si>
-    <t>RADIOTHERAPIE</t>
-  </si>
-  <si>
-    <t>136</t>
-  </si>
-  <si>
-    <t>Médecine Nucléaire</t>
-  </si>
-  <si>
-    <t>137</t>
-  </si>
-  <si>
-    <t>138</t>
-  </si>
-  <si>
-    <t>141</t>
-  </si>
-  <si>
-    <t>Réanimation Chirurgicale Adultes</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>SPECIALITE CHIRURGICALE</t>
-  </si>
-  <si>
-    <t>144</t>
-  </si>
-  <si>
-    <t>Chirurgie Carcinologie</t>
-  </si>
-  <si>
-    <t>145</t>
-  </si>
-  <si>
-    <t>Traitement des Grands Brûlés</t>
-  </si>
-  <si>
-    <t>146</t>
-  </si>
-  <si>
-    <t>Chirurgie Digestive</t>
-  </si>
-  <si>
-    <t>147</t>
-  </si>
-  <si>
-    <t>Chirurgie Thoracique Cardio-Vasculaire</t>
-  </si>
-  <si>
-    <t>148</t>
-  </si>
-  <si>
-    <t>CHIRURGIE THORACO-PULMONAIRE</t>
-  </si>
-  <si>
-    <t>149</t>
-  </si>
-  <si>
-    <t>Chirurgie Vasculaire</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>CHIRURGIE CARDIO-VASCULAIRE</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>Neurochirurgie</t>
-  </si>
-  <si>
-    <t>152</t>
-  </si>
-  <si>
-    <t>Orthopédie-Traumatologie</t>
-  </si>
-  <si>
-    <t>153</t>
-  </si>
-  <si>
-    <t>Actes d'explantation de prothèses PIP</t>
-  </si>
-  <si>
-    <t>154</t>
-  </si>
-  <si>
-    <t>Chirurgie Plastique Reconstructive</t>
-  </si>
-  <si>
-    <t>155</t>
-  </si>
-  <si>
-    <t>ORL ET OPHTALMOLOGIE</t>
-  </si>
-  <si>
-    <t>156</t>
-  </si>
-  <si>
-    <t>Oto-rhino-laryngologie</t>
-  </si>
-  <si>
-    <t>157</t>
-  </si>
-  <si>
-    <t>Ophtalmologie</t>
-  </si>
-  <si>
-    <t>158</t>
-  </si>
-  <si>
-    <t>Stomatologie Chirurgie Maxillo-faciale</t>
-  </si>
-  <si>
-    <t>159</t>
-  </si>
-  <si>
-    <t>Stomatologie</t>
-  </si>
-  <si>
-    <t>161</t>
-  </si>
-  <si>
-    <t>Urologie</t>
-  </si>
-  <si>
-    <t>162</t>
-  </si>
-  <si>
-    <t>ORL-OPHTALMOLOG.&amp; STOMATOLOGIE</t>
-  </si>
-  <si>
-    <t>163</t>
-  </si>
-  <si>
-    <t>Gynéco.&amp; Obstétrique</t>
-  </si>
-  <si>
-    <t>164</t>
-  </si>
-  <si>
-    <t>Gynécologie Médicale</t>
-  </si>
-  <si>
-    <t>165</t>
-  </si>
-  <si>
-    <t>166</t>
-  </si>
-  <si>
-    <t>Chroniques Convalescence Indifférencié</t>
-  </si>
-  <si>
-    <t>167</t>
-  </si>
-  <si>
-    <t>Chroniques</t>
-  </si>
-  <si>
-    <t>168</t>
-  </si>
-  <si>
-    <t>Repos-Convalescence Régime Indifférencié</t>
-  </si>
-  <si>
-    <t>169</t>
-  </si>
-  <si>
-    <t>Repos</t>
-  </si>
-  <si>
-    <t>170</t>
-  </si>
-  <si>
-    <t>Convalescence</t>
-  </si>
-  <si>
-    <t>171</t>
-  </si>
-  <si>
-    <t>Régime</t>
-  </si>
-  <si>
-    <t>172</t>
-  </si>
-  <si>
-    <t>Rééducation Fonctionnelle Réadaptation Polyvalente</t>
-  </si>
-  <si>
-    <t>173</t>
-  </si>
-  <si>
-    <t>Cure Thermale</t>
-  </si>
-  <si>
-    <t>174</t>
-  </si>
-  <si>
-    <t>MEDEC.GEN. &amp; SPECIALITE MEDIC.</t>
-  </si>
-  <si>
-    <t>176</t>
-  </si>
-  <si>
-    <t>Long Séjour Personnes Ayant Perdu Leur Autonomie de Vie</t>
-  </si>
-  <si>
-    <t>178</t>
-  </si>
-  <si>
-    <t>Rééducation Fonctionnelle Réadaptation Motrice</t>
-  </si>
-  <si>
-    <t>179</t>
-  </si>
-  <si>
-    <t>Rééducation Fonctionnelle Réadaptation Neurologique</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>Rééducation des Affections Respiratoires</t>
-  </si>
-  <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>Chirurgie Générale Spécialités Chirurgicales</t>
-  </si>
-  <si>
-    <t>182</t>
-  </si>
-  <si>
-    <t>Rééducat. Maladies Cardio-Vasculaires</t>
-  </si>
-  <si>
-    <t>183</t>
-  </si>
-  <si>
-    <t>OBSTETRIQUE SANS CHIRURGIE</t>
-  </si>
-  <si>
-    <t>184</t>
-  </si>
-  <si>
-    <t>Rééducation des Affections Hépato-Digestives</t>
-  </si>
-  <si>
-    <t>185</t>
-  </si>
-  <si>
-    <t>Repos-Convalescence Indifférenciés</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>REEDUCATION PERSONNE AGEE</t>
-  </si>
-  <si>
-    <t>187</t>
-  </si>
-  <si>
-    <t>Rééducation Fonctionnelle Réadaptation</t>
-  </si>
-  <si>
-    <t>189</t>
-  </si>
-  <si>
-    <t>Cure Thermale des Voies Respiratoires</t>
-  </si>
-  <si>
-    <t>191</t>
-  </si>
-  <si>
-    <t>CURE THERM.AFFECT.HEPATO-DIGES</t>
-  </si>
-  <si>
-    <t>192</t>
-  </si>
-  <si>
-    <t>CURE THERM.APPAREIL URINAIRE</t>
-  </si>
-  <si>
-    <t>193</t>
-  </si>
-  <si>
-    <t>Cure Thermale Rhumatologie Séquel.Traum.Ostéo-articaires</t>
-  </si>
-  <si>
-    <t>194</t>
-  </si>
-  <si>
-    <t>Cure Thermale en Dermatologie</t>
-  </si>
-  <si>
-    <t>195</t>
-  </si>
-  <si>
-    <t>Soins aux Toxicomanes</t>
-  </si>
-  <si>
-    <t>196</t>
-  </si>
-  <si>
-    <t>Lutte Contre l'Alcoolisme</t>
-  </si>
-  <si>
-    <t>197</t>
-  </si>
-  <si>
-    <t>Activité dentaire unique</t>
-  </si>
-  <si>
-    <t>198</t>
-  </si>
-  <si>
-    <t>Oncologie</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>Transfusion Sanguine (Laboratoire)</t>
-  </si>
-  <si>
-    <t>201</t>
-  </si>
-  <si>
-    <t>Banque de Sperme</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>Banque d'Organes</t>
-  </si>
-  <si>
-    <t>203</t>
-  </si>
-  <si>
-    <t>Dispensaire de Soins</t>
-  </si>
-  <si>
-    <t>204</t>
-  </si>
-  <si>
-    <t>Activité infirmière unique</t>
-  </si>
-  <si>
-    <t>205</t>
-  </si>
-  <si>
-    <t>Act inform dépistage diag infections sexuellmnt transmissibl</t>
-  </si>
-  <si>
-    <t>206</t>
-  </si>
-  <si>
-    <t>Lutte Antihansénienne</t>
-  </si>
-  <si>
-    <t>207</t>
-  </si>
-  <si>
-    <t>S.A.M.U Centre 15</t>
-  </si>
-  <si>
-    <t>208</t>
-  </si>
-  <si>
-    <t>S.M.U.R. U.M.H.</t>
-  </si>
-  <si>
-    <t>209</t>
-  </si>
-  <si>
-    <t>Ambulances</t>
-  </si>
-  <si>
-    <t>211</t>
-  </si>
-  <si>
-    <t>Accueil et Traitement des Urgences Médico-Chirurgicales</t>
-  </si>
-  <si>
-    <t>214</t>
-  </si>
-  <si>
-    <t>Postcure pour Alcooliques</t>
-  </si>
-  <si>
-    <t>217</t>
-  </si>
-  <si>
-    <t>Lutte Contre La Tuberculose Indifférenciée</t>
-  </si>
-  <si>
-    <t>218</t>
-  </si>
-  <si>
-    <t>Activité de lutte anti tuberculose</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>Lutte Ctre la Tuberculose Pulmonaire</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>Lutte Ctre Tuberculose Extra-Pulmonaire</t>
-  </si>
-  <si>
-    <t>221</t>
-  </si>
-  <si>
-    <t>Cure et Repos en Prévention</t>
-  </si>
-  <si>
-    <t>222</t>
-  </si>
-  <si>
-    <t>Traitements Préventifs de la Tuberculose</t>
-  </si>
-  <si>
-    <t>223</t>
-  </si>
-  <si>
-    <t>Médecine Générale ou Polyvalente</t>
-  </si>
-  <si>
-    <t>224</t>
-  </si>
-  <si>
-    <t>Observation et Traitement Pneumoconioses</t>
-  </si>
-  <si>
-    <t>225</t>
-  </si>
-  <si>
-    <t>Médecine Interne Spécialités Médicales</t>
-  </si>
-  <si>
-    <t>226</t>
-  </si>
-  <si>
-    <t>Accueil Orientation. des Malades.Tuberculo Pulmonaires</t>
-  </si>
-  <si>
-    <t>227</t>
-  </si>
-  <si>
-    <t>Postcure pour Tuberculeux</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>Psychiatrie Générale</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>centre médico-psychologique adulte</t>
-  </si>
-  <si>
-    <t>232</t>
-  </si>
-  <si>
-    <t>centre médico-psychologique infanto-juvénile</t>
-  </si>
-  <si>
-    <t>233</t>
-  </si>
-  <si>
-    <t>Centre d'accueil thérapeutique à temps partiel adulte</t>
-  </si>
-  <si>
-    <t>234</t>
-  </si>
-  <si>
-    <t>Centre d'accueil thérapeutique à temps partiel infanto-juv</t>
-  </si>
-  <si>
-    <t>235</t>
-  </si>
-  <si>
-    <t>soins intensifs de néonatologie</t>
-  </si>
-  <si>
-    <t>236</t>
-  </si>
-  <si>
-    <t>Psychiatrie Infanto-Juvenile</t>
-  </si>
-  <si>
-    <t>237</t>
-  </si>
-  <si>
-    <t>centre d'accueil permanent adulte</t>
-  </si>
-  <si>
-    <t>238</t>
-  </si>
-  <si>
-    <t>centre d'accueil permanent infanto-juvénile</t>
-  </si>
-  <si>
-    <t>240</t>
-  </si>
-  <si>
-    <t>POST-CURE POUR TOXICOMANES</t>
-  </si>
-  <si>
-    <t>241</t>
-  </si>
-  <si>
-    <t>Hygiène Alimentaire</t>
-  </si>
-  <si>
-    <t>244</t>
-  </si>
-  <si>
-    <t>hospitalisation psychiatrique à domicile adulte</t>
-  </si>
-  <si>
-    <t>245</t>
-  </si>
-  <si>
-    <t>hospitalisation psychiatrique à domicile infanto-juv</t>
-  </si>
-  <si>
-    <t>252</t>
-  </si>
-  <si>
-    <t>Pouponnière à Caractère Sanitaire</t>
-  </si>
-  <si>
-    <t>263</t>
-  </si>
-  <si>
-    <t>Placement familial sanitaire</t>
-  </si>
-  <si>
-    <t>265</t>
-  </si>
-  <si>
-    <t>COLONIE A CARACTERE SANITAIRE</t>
-  </si>
-  <si>
-    <t>302</t>
-  </si>
-  <si>
-    <t>CHIMIOTHER.EN HEMATOL.&amp; CANCER</t>
-  </si>
-  <si>
-    <t>303</t>
-  </si>
-  <si>
-    <t>Urgence Médicale</t>
-  </si>
-  <si>
-    <t>307</t>
-  </si>
-  <si>
-    <t>Urgence Chirurgicale (SERV.PORTE)</t>
-  </si>
-  <si>
-    <t>308</t>
-  </si>
-  <si>
-    <t>Urgence Indifférenciée</t>
-  </si>
-  <si>
-    <t>309</t>
-  </si>
-  <si>
-    <t>Interruption Volontaire de Grossesse</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Examens de Santé et Bilans</t>
-  </si>
-  <si>
-    <t>312</t>
-  </si>
-  <si>
-    <t>Néphrologie</t>
-  </si>
-  <si>
-    <t>362</t>
-  </si>
-  <si>
-    <t>Chirurgie Obstétrique Indifférenciées</t>
-  </si>
-  <si>
-    <t>384</t>
-  </si>
-  <si>
-    <t>Protection Maternelle &amp; Infantile</t>
-  </si>
-  <si>
-    <t>385</t>
-  </si>
-  <si>
-    <t>Consultations Prénuptiale Prénatale et Postnatale</t>
-  </si>
-  <si>
-    <t>386</t>
-  </si>
-  <si>
-    <t>Consultations Protection Infantile</t>
-  </si>
-  <si>
-    <t>387</t>
-  </si>
-  <si>
-    <t>Consultations de Nourrissons</t>
-  </si>
-  <si>
-    <t>388</t>
-  </si>
-  <si>
-    <t>Consultations de deuxième age</t>
-  </si>
-  <si>
-    <t>389</t>
-  </si>
-  <si>
-    <t>Lutte contre la Stérilité</t>
-  </si>
-  <si>
-    <t>390</t>
-  </si>
-  <si>
-    <t>Consultation en Conseil Génétique</t>
-  </si>
-  <si>
-    <t>391</t>
-  </si>
-  <si>
-    <t>Consultation de Planification ou Éducation Familiale</t>
-  </si>
-  <si>
-    <t>392</t>
-  </si>
-  <si>
-    <t>Information Consultation ou Conseil familial</t>
-  </si>
-  <si>
-    <t>394</t>
-  </si>
-  <si>
-    <t>Lactarium</t>
-  </si>
-  <si>
-    <t>395</t>
-  </si>
-  <si>
-    <t>Guidance Parentale</t>
-  </si>
-  <si>
-    <t>396</t>
-  </si>
-  <si>
-    <t>Guidance infantile</t>
-  </si>
-  <si>
-    <t>401</t>
-  </si>
-  <si>
-    <t>unité de proximité accueil traitement orientation urgences</t>
-  </si>
-  <si>
-    <t>402</t>
-  </si>
-  <si>
-    <t>service accueil et traitement urgences</t>
-  </si>
-  <si>
-    <t>403</t>
-  </si>
-  <si>
-    <t>pôle spécialisé urgence en pédiatrie</t>
-  </si>
-  <si>
-    <t>404</t>
-  </si>
-  <si>
-    <t>pôle spécialisé urgence en ophtalmologie</t>
-  </si>
-  <si>
-    <t>405</t>
-  </si>
-  <si>
-    <t>pôle spécialisé urgence en cardiologie</t>
-  </si>
-  <si>
-    <t>406</t>
-  </si>
-  <si>
-    <t>pôle spécialisé urgence en traumatologie</t>
-  </si>
-  <si>
-    <t>407</t>
-  </si>
-  <si>
-    <t>pôle spécialisé urgence en SOS main</t>
-  </si>
-  <si>
-    <t>408</t>
-  </si>
-  <si>
-    <t>pôle spécialisé urgence en neurochirurgie</t>
-  </si>
-  <si>
-    <t>409</t>
-  </si>
-  <si>
-    <t>autre pôle spécialisé urgence non dénommé ailleurs</t>
-  </si>
-  <si>
-    <t>446</t>
-  </si>
-  <si>
-    <t>Médecine Scolaire</t>
-  </si>
-  <si>
-    <t>447</t>
-  </si>
-  <si>
-    <t>Médecine Universitaire</t>
-  </si>
-  <si>
-    <t>448</t>
-  </si>
-  <si>
-    <t>Médecine Sportive</t>
-  </si>
-  <si>
-    <t>452</t>
-  </si>
-  <si>
-    <t>Aide Aux Insuffisants Respiratoires</t>
-  </si>
-  <si>
     <t>Cure Médic.Spécialisée Contre Tuberculose Indifférenciée</t>
   </si>
   <si>
@@ -2816,6 +2819,42 @@
   </si>
   <si>
     <t>Activité sage-femme en maison de naissance</t>
+  </si>
+  <si>
+    <t>855</t>
+  </si>
+  <si>
+    <t>Maison médicale de garde</t>
+  </si>
+  <si>
+    <t>Activités contribuant à la permanence des Soins Ambulatoires (PDSA) exercées dans le cadre d'une Maison Médicale de Garde</t>
+  </si>
+  <si>
+    <t>856</t>
+  </si>
+  <si>
+    <t>Point fixe de garde</t>
+  </si>
+  <si>
+    <t>Activités contribuant à la permanence des Soins Ambulatoires (PDSA) exercées dans le cadre d'un Point fixe de garde</t>
+  </si>
+  <si>
+    <t>857</t>
+  </si>
+  <si>
+    <t>Point fixe de consultation</t>
+  </si>
+  <si>
+    <t>Activités contribuant à la permanence des Soins Ambulatoires (PDSA) exercées dans le cadre d'un Point fixe de consultation</t>
+  </si>
+  <si>
+    <t>858</t>
+  </si>
+  <si>
+    <t>Visite à domicile</t>
+  </si>
+  <si>
+    <t>Activités contribuant à la permanence des Soins Ambulatoires (PDSA) exercées dans le cadre de visites à domicile</t>
   </si>
   <si>
     <t>949</t>
@@ -3311,7 +3350,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D458"/>
+  <dimension ref="A1:D462"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -7029,10 +7068,10 @@
         <v>70</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>36</v>
+        <v>654</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D310" s="2"/>
     </row>
@@ -7041,10 +7080,10 @@
         <v>70</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D311" s="2"/>
     </row>
@@ -7053,10 +7092,10 @@
         <v>70</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D312" s="2"/>
     </row>
@@ -7065,10 +7104,10 @@
         <v>70</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D313" s="2"/>
     </row>
@@ -7077,10 +7116,10 @@
         <v>70</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D314" s="2"/>
     </row>
@@ -7089,10 +7128,10 @@
         <v>70</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D315" s="2"/>
     </row>
@@ -7101,10 +7140,10 @@
         <v>70</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D316" s="2"/>
     </row>
@@ -7113,10 +7152,10 @@
         <v>70</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D317" s="2"/>
     </row>
@@ -7125,10 +7164,10 @@
         <v>70</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D318" s="2"/>
     </row>
@@ -7137,10 +7176,10 @@
         <v>70</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D319" s="2"/>
     </row>
@@ -7149,10 +7188,10 @@
         <v>70</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D320" s="2"/>
     </row>
@@ -7161,10 +7200,10 @@
         <v>70</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D321" s="2"/>
     </row>
@@ -7173,10 +7212,10 @@
         <v>70</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D322" s="2"/>
     </row>
@@ -7185,10 +7224,10 @@
         <v>70</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D323" s="2"/>
     </row>
@@ -7197,10 +7236,10 @@
         <v>70</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D324" s="2"/>
     </row>
@@ -7209,10 +7248,10 @@
         <v>70</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D325" s="2"/>
     </row>
@@ -7221,10 +7260,10 @@
         <v>70</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D326" s="2"/>
     </row>
@@ -7233,10 +7272,10 @@
         <v>70</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D327" s="2"/>
     </row>
@@ -7245,10 +7284,10 @@
         <v>70</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D328" s="2"/>
     </row>
@@ -7257,10 +7296,10 @@
         <v>70</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D329" s="2"/>
     </row>
@@ -7269,10 +7308,10 @@
         <v>70</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D330" s="2"/>
     </row>
@@ -7281,10 +7320,10 @@
         <v>70</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D331" s="2"/>
     </row>
@@ -7293,10 +7332,10 @@
         <v>70</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D332" s="2"/>
     </row>
@@ -7305,10 +7344,10 @@
         <v>70</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D333" s="2"/>
     </row>
@@ -7317,10 +7356,10 @@
         <v>70</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D334" s="2"/>
     </row>
@@ -7329,10 +7368,10 @@
         <v>70</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D335" s="2"/>
     </row>
@@ -7341,10 +7380,10 @@
         <v>70</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D336" s="2"/>
     </row>
@@ -7353,10 +7392,10 @@
         <v>70</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D337" s="2"/>
     </row>
@@ -7365,10 +7404,10 @@
         <v>70</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D338" s="2"/>
     </row>
@@ -7377,10 +7416,10 @@
         <v>70</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D339" s="2"/>
     </row>
@@ -7389,10 +7428,10 @@
         <v>70</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D340" s="2"/>
     </row>
@@ -7401,10 +7440,10 @@
         <v>70</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D341" s="2"/>
     </row>
@@ -7413,10 +7452,10 @@
         <v>70</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D342" s="2"/>
     </row>
@@ -7425,10 +7464,10 @@
         <v>70</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D343" s="2"/>
     </row>
@@ -7437,10 +7476,10 @@
         <v>70</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D344" s="2"/>
     </row>
@@ -7449,10 +7488,10 @@
         <v>70</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D345" s="2"/>
     </row>
@@ -7461,10 +7500,10 @@
         <v>70</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D346" s="2"/>
     </row>
@@ -7473,10 +7512,10 @@
         <v>70</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D347" s="2"/>
     </row>
@@ -7485,10 +7524,10 @@
         <v>70</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D348" s="2"/>
     </row>
@@ -7497,10 +7536,10 @@
         <v>70</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D349" s="2"/>
     </row>
@@ -7509,10 +7548,10 @@
         <v>70</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D350" s="2"/>
     </row>
@@ -7521,10 +7560,10 @@
         <v>70</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D351" s="2"/>
     </row>
@@ -7533,10 +7572,10 @@
         <v>70</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D352" s="2"/>
     </row>
@@ -7545,10 +7584,10 @@
         <v>70</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D353" s="2"/>
     </row>
@@ -7557,10 +7596,10 @@
         <v>70</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D354" s="2"/>
     </row>
@@ -7569,10 +7608,10 @@
         <v>70</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D355" s="2"/>
     </row>
@@ -7581,10 +7620,10 @@
         <v>70</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D356" s="2"/>
     </row>
@@ -7593,10 +7632,10 @@
         <v>70</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D357" s="2"/>
     </row>
@@ -7605,10 +7644,10 @@
         <v>70</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D358" s="2"/>
     </row>
@@ -7617,10 +7656,10 @@
         <v>70</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D359" s="2"/>
     </row>
@@ -7629,10 +7668,10 @@
         <v>70</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D360" s="2"/>
     </row>
@@ -7641,10 +7680,10 @@
         <v>70</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D361" s="2"/>
     </row>
@@ -7653,10 +7692,10 @@
         <v>70</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D362" s="2"/>
     </row>
@@ -7665,10 +7704,10 @@
         <v>70</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D363" s="2"/>
     </row>
@@ -7677,10 +7716,10 @@
         <v>70</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D364" s="2"/>
     </row>
@@ -7689,10 +7728,10 @@
         <v>70</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D365" s="2"/>
     </row>
@@ -7701,10 +7740,10 @@
         <v>70</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D366" s="2"/>
     </row>
@@ -7713,10 +7752,10 @@
         <v>70</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D367" s="2"/>
     </row>
@@ -7725,10 +7764,10 @@
         <v>70</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D368" s="2"/>
     </row>
@@ -7737,10 +7776,10 @@
         <v>70</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D369" s="2"/>
     </row>
@@ -7749,10 +7788,10 @@
         <v>70</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D370" s="2"/>
     </row>
@@ -7761,10 +7800,10 @@
         <v>70</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D371" s="2"/>
     </row>
@@ -7773,10 +7812,10 @@
         <v>70</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D372" s="2"/>
     </row>
@@ -7785,10 +7824,10 @@
         <v>70</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D373" s="2"/>
     </row>
@@ -7797,10 +7836,10 @@
         <v>70</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D374" s="2"/>
     </row>
@@ -7809,10 +7848,10 @@
         <v>70</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D375" s="2"/>
     </row>
@@ -7821,10 +7860,10 @@
         <v>70</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D376" s="2"/>
     </row>
@@ -7833,10 +7872,10 @@
         <v>70</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D377" s="2"/>
     </row>
@@ -7845,10 +7884,10 @@
         <v>70</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D378" s="2"/>
     </row>
@@ -7857,10 +7896,10 @@
         <v>70</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D379" s="2"/>
     </row>
@@ -7869,10 +7908,10 @@
         <v>70</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D380" s="2"/>
     </row>
@@ -7881,10 +7920,10 @@
         <v>70</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D381" s="2"/>
     </row>
@@ -7893,10 +7932,10 @@
         <v>70</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D382" s="2"/>
     </row>
@@ -7905,10 +7944,10 @@
         <v>70</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D383" s="2"/>
     </row>
@@ -7917,10 +7956,10 @@
         <v>70</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D384" s="2"/>
     </row>
@@ -7929,10 +7968,10 @@
         <v>70</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D385" s="2"/>
     </row>
@@ -7941,10 +7980,10 @@
         <v>70</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D386" s="2"/>
     </row>
@@ -7953,10 +7992,10 @@
         <v>70</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D387" s="2"/>
     </row>
@@ -7965,10 +8004,10 @@
         <v>70</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D388" s="2"/>
     </row>
@@ -7977,10 +8016,10 @@
         <v>70</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D389" s="2"/>
     </row>
@@ -7989,10 +8028,10 @@
         <v>70</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D390" s="2"/>
     </row>
@@ -8001,10 +8040,10 @@
         <v>70</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D391" s="2"/>
     </row>
@@ -8013,10 +8052,10 @@
         <v>70</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D392" s="2"/>
     </row>
@@ -8025,10 +8064,10 @@
         <v>70</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D393" s="2"/>
     </row>
@@ -8037,10 +8076,10 @@
         <v>70</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D394" s="2"/>
     </row>
@@ -8049,10 +8088,10 @@
         <v>70</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D395" s="2"/>
     </row>
@@ -8061,10 +8100,10 @@
         <v>70</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D396" s="2"/>
     </row>
@@ -8073,10 +8112,10 @@
         <v>70</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D397" s="2"/>
     </row>
@@ -8085,10 +8124,10 @@
         <v>70</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D398" s="2"/>
     </row>
@@ -8097,10 +8136,10 @@
         <v>70</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D399" s="2"/>
     </row>
@@ -8109,10 +8148,10 @@
         <v>70</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D400" s="2"/>
     </row>
@@ -8121,10 +8160,10 @@
         <v>70</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D401" s="2"/>
     </row>
@@ -8133,10 +8172,10 @@
         <v>70</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D402" s="2"/>
     </row>
@@ -8145,10 +8184,10 @@
         <v>70</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D403" s="2"/>
     </row>
@@ -8157,10 +8196,10 @@
         <v>70</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D404" s="2"/>
     </row>
@@ -8169,10 +8208,10 @@
         <v>70</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D405" s="2"/>
     </row>
@@ -8181,10 +8220,10 @@
         <v>70</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="D406" s="2"/>
     </row>
@@ -8193,10 +8232,10 @@
         <v>70</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D407" s="2"/>
     </row>
@@ -8205,10 +8244,10 @@
         <v>70</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D408" s="2"/>
     </row>
@@ -8217,10 +8256,10 @@
         <v>70</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="D409" s="2"/>
     </row>
@@ -8229,10 +8268,10 @@
         <v>70</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D410" s="2"/>
     </row>
@@ -8241,10 +8280,10 @@
         <v>70</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D411" s="2"/>
     </row>
@@ -8253,10 +8292,10 @@
         <v>70</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D412" s="2"/>
     </row>
@@ -8265,10 +8304,10 @@
         <v>70</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="D413" s="2"/>
     </row>
@@ -8277,10 +8316,10 @@
         <v>70</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D414" s="2"/>
     </row>
@@ -8289,10 +8328,10 @@
         <v>70</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D415" s="2"/>
     </row>
@@ -8301,10 +8340,10 @@
         <v>70</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D416" s="2"/>
     </row>
@@ -8313,10 +8352,10 @@
         <v>70</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D417" s="2"/>
     </row>
@@ -8325,10 +8364,10 @@
         <v>70</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D418" s="2"/>
     </row>
@@ -8337,7 +8376,7 @@
         <v>70</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C419" t="s" s="2">
         <v>110</v>
@@ -8349,10 +8388,10 @@
         <v>70</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D420" s="2"/>
     </row>
@@ -8361,10 +8400,10 @@
         <v>70</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D421" s="2"/>
     </row>
@@ -8373,10 +8412,10 @@
         <v>70</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="D422" s="2"/>
     </row>
@@ -8385,10 +8424,10 @@
         <v>70</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D423" s="2"/>
     </row>
@@ -8397,10 +8436,10 @@
         <v>70</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D424" s="2"/>
     </row>
@@ -8409,10 +8448,10 @@
         <v>70</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C425" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D425" s="2"/>
     </row>
@@ -8421,10 +8460,10 @@
         <v>70</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="D426" s="2"/>
     </row>
@@ -8433,10 +8472,10 @@
         <v>70</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D427" s="2"/>
     </row>
@@ -8445,10 +8484,10 @@
         <v>70</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D428" s="2"/>
     </row>
@@ -8457,10 +8496,10 @@
         <v>70</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C429" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D429" s="2"/>
     </row>
@@ -8469,10 +8508,10 @@
         <v>70</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C430" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D430" s="2"/>
     </row>
@@ -8481,10 +8520,10 @@
         <v>70</v>
       </c>
       <c r="B431" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C431" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D431" s="2"/>
     </row>
@@ -8493,10 +8532,10 @@
         <v>70</v>
       </c>
       <c r="B432" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C432" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="D432" s="2"/>
     </row>
@@ -8505,10 +8544,10 @@
         <v>70</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C433" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D433" s="2"/>
     </row>
@@ -8517,10 +8556,10 @@
         <v>70</v>
       </c>
       <c r="B434" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C434" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D434" s="2"/>
     </row>
@@ -8529,10 +8568,10 @@
         <v>70</v>
       </c>
       <c r="B435" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C435" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D435" s="2"/>
     </row>
@@ -8541,10 +8580,10 @@
         <v>70</v>
       </c>
       <c r="B436" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C436" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D436" s="2"/>
     </row>
@@ -8553,10 +8592,10 @@
         <v>70</v>
       </c>
       <c r="B437" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C437" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D437" s="2"/>
     </row>
@@ -8565,10 +8604,10 @@
         <v>70</v>
       </c>
       <c r="B438" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C438" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D438" s="2"/>
     </row>
@@ -8577,10 +8616,10 @@
         <v>70</v>
       </c>
       <c r="B439" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C439" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D439" s="2"/>
     </row>
@@ -8589,10 +8628,10 @@
         <v>70</v>
       </c>
       <c r="B440" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C440" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D440" s="2"/>
     </row>
@@ -8601,10 +8640,10 @@
         <v>70</v>
       </c>
       <c r="B441" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C441" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D441" s="2"/>
     </row>
@@ -8613,10 +8652,10 @@
         <v>70</v>
       </c>
       <c r="B442" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C442" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D442" s="2"/>
     </row>
@@ -8625,10 +8664,10 @@
         <v>70</v>
       </c>
       <c r="B443" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C443" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D443" s="2"/>
     </row>
@@ -8637,10 +8676,10 @@
         <v>70</v>
       </c>
       <c r="B444" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C444" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D444" s="2"/>
     </row>
@@ -8649,10 +8688,10 @@
         <v>70</v>
       </c>
       <c r="B445" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C445" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D445" s="2"/>
     </row>
@@ -8661,10 +8700,10 @@
         <v>70</v>
       </c>
       <c r="B446" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C446" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="D446" s="2"/>
     </row>
@@ -8673,10 +8712,10 @@
         <v>70</v>
       </c>
       <c r="B447" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="C447" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D447" s="2"/>
     </row>
@@ -8685,10 +8724,10 @@
         <v>70</v>
       </c>
       <c r="B448" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C448" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D448" s="2"/>
     </row>
@@ -8697,10 +8736,10 @@
         <v>70</v>
       </c>
       <c r="B449" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C449" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D449" s="2"/>
     </row>
@@ -8709,10 +8748,10 @@
         <v>70</v>
       </c>
       <c r="B450" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C450" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D450" s="2"/>
     </row>
@@ -8721,58 +8760,66 @@
         <v>70</v>
       </c>
       <c r="B451" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C451" t="s" s="2">
-        <v>935</v>
-      </c>
-      <c r="D451" s="2"/>
+        <v>936</v>
+      </c>
+      <c r="D451" t="s" s="2">
+        <v>937</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="s" s="2">
         <v>70</v>
       </c>
       <c r="B452" t="s" s="2">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="C452" t="s" s="2">
-        <v>937</v>
-      </c>
-      <c r="D452" s="2"/>
+        <v>939</v>
+      </c>
+      <c r="D452" t="s" s="2">
+        <v>940</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="s" s="2">
         <v>70</v>
       </c>
       <c r="B453" t="s" s="2">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="C453" t="s" s="2">
-        <v>939</v>
-      </c>
-      <c r="D453" s="2"/>
+        <v>942</v>
+      </c>
+      <c r="D453" t="s" s="2">
+        <v>943</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="s" s="2">
         <v>70</v>
       </c>
       <c r="B454" t="s" s="2">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="C454" t="s" s="2">
-        <v>941</v>
-      </c>
-      <c r="D454" s="2"/>
+        <v>945</v>
+      </c>
+      <c r="D454" t="s" s="2">
+        <v>946</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="s" s="2">
         <v>70</v>
       </c>
       <c r="B455" t="s" s="2">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="C455" t="s" s="2">
-        <v>943</v>
+        <v>948</v>
       </c>
       <c r="D455" s="2"/>
     </row>
@@ -8781,10 +8828,10 @@
         <v>70</v>
       </c>
       <c r="B456" t="s" s="2">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="C456" t="s" s="2">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="D456" s="2"/>
     </row>
@@ -8793,10 +8840,10 @@
         <v>70</v>
       </c>
       <c r="B457" t="s" s="2">
-        <v>946</v>
+        <v>951</v>
       </c>
       <c r="C457" t="s" s="2">
-        <v>947</v>
+        <v>952</v>
       </c>
       <c r="D457" s="2"/>
     </row>
@@ -8805,12 +8852,60 @@
         <v>70</v>
       </c>
       <c r="B458" t="s" s="2">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="C458" t="s" s="2">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="D458" s="2"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B459" t="s" s="2">
+        <v>955</v>
+      </c>
+      <c r="C459" t="s" s="2">
+        <v>956</v>
+      </c>
+      <c r="D459" s="2"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B460" t="s" s="2">
+        <v>957</v>
+      </c>
+      <c r="C460" t="s" s="2">
+        <v>958</v>
+      </c>
+      <c r="D460" s="2"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B461" t="s" s="2">
+        <v>959</v>
+      </c>
+      <c r="C461" t="s" s="2">
+        <v>960</v>
+      </c>
+      <c r="D461" s="2"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B462" t="s" s="2">
+        <v>961</v>
+      </c>
+      <c r="C462" t="s" s="2">
+        <v>962</v>
+      </c>
+      <c r="D462" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
